--- a/docs/CodeSystem-retina-imagequality-cs.xlsx
+++ b/docs/CodeSystem-retina-imagequality-cs.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Image Quality CodeSystem for Retinascreening</t>
+    <t>Image Quality</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-08T17:39:22+01:00</t>
+    <t>2025-11-11T17:38:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Image quality as interpreted by an AI solution.</t>
+    <t>Image quality as interpreted by an AI solution. (2000-series)</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/CodeSystem-retina-imagequality-cs.xlsx
+++ b/docs/CodeSystem-retina-imagequality-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-11T17:38:50+01:00</t>
+    <t>2025-11-12T18:21:01+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-retina-imagequality-cs.xlsx
+++ b/docs/CodeSystem-retina-imagequality-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-12T18:21:01+01:00</t>
+    <t>2025-11-13T17:39:30+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-retina-imagequality-cs.xlsx
+++ b/docs/CodeSystem-retina-imagequality-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-11T17:38:50+01:00</t>
+    <t>2025-11-15T17:14:08+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-retina-imagequality-cs.xlsx
+++ b/docs/CodeSystem-retina-imagequality-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-15T17:14:08+01:00</t>
+    <t>2025-11-16T16:39:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CodeSystem-retina-imagequality-cs.xlsx
+++ b/docs/CodeSystem-retina-imagequality-cs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.3</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -42,13 +42,13 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Image Quality</t>
+    <t>Retina Image Quality</t>
   </si>
   <si>
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-13T17:39:30+01:00</t>
+    <t>2025-11-30T22:57:21+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Image quality as interpreted by an AI solution. (2000-series)</t>
+    <t>Image quality as asessed by AI solution (2000-series).</t>
   </si>
   <si>
     <t>Purpose</t>
